--- a/diseases/d008/1995-1999.xlsx
+++ b/diseases/d008/1995-1999.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,90 +751,101 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>1400</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -866,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -896,35 +907,38 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>1400</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1400</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Lifrarbólga B (bráð, viðvarandi)</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -934,7 +948,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -949,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -959,22 +973,22 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>related</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -984,12 +998,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual reported aggregate combining acute and persistent hepatitis B; it is retained as related to course-unspecified D008 but is not interchangeable with a single-course series. Published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -998,7 +1012,7 @@
         </is>
       </c>
       <c r="AN3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1017,11 +1031,11 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1030,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1092,17 +1106,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1127,176 +1141,101 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1222</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1222</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1262,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1358,90 +1297,179 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>1222</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>1222</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1468,17 +1496,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1503,176 +1531,101 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1018</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1018</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1652,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1734,90 +1687,179 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>1018</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>1018</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1886,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1879,176 +1921,90 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN8" t="b">
+        <v>16</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -2075,17 +2031,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2110,90 +2066,176 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q9" t="n">
+        <v>21</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B (bráð, viðvarandi)</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual reported aggregate combining acute and persistent hepatitis B; it is retained as related to course-unspecified D008 but is not interchangeable with a single-course series. Published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2255,16 +2297,16 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2486,19 +2528,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2631,12 +2673,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2862,19 +2904,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -3007,16 +3049,16 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3238,12 +3280,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3383,16 +3425,16 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3614,19 +3656,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3759,16 +3801,16 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3990,19 +4032,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -4135,12 +4177,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4366,19 +4408,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4511,12 +4553,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4742,19 +4784,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4887,16 +4929,16 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -5118,19 +5160,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -5263,16 +5305,16 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -5494,19 +5536,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5639,25 +5681,25 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -5667,7 +5709,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Lifrarbólga B (bráð, viðvarandi)</t>
+          <t>Lifrarbólga B</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -5682,7 +5724,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -5712,7 +5754,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -5727,12 +5769,12 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>IS_DOH_disease_specific_monthly</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual reported aggregate combining acute and persistent hepatitis B; it is retained as related to course-unspecified D008 but is not interchangeable with a single-course series. Published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -5835,17 +5877,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5870,176 +5912,90 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN29" t="b">
+        <v>11</v>
+      </c>
+      <c r="O29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6066,17 +6022,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6101,90 +6057,176 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN30" t="b">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6211,17 +6253,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6246,176 +6288,90 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="n">
         <v>0</v>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN31" t="b">
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AT31" t="n">
-        <v>3</v>
-      </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6442,17 +6398,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6477,90 +6433,176 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
-      </c>
-      <c r="O32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN32" t="b">
+        <v>0</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6587,17 +6629,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6622,176 +6664,101 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>938</v>
+      </c>
+      <c r="O33" t="n">
+        <v>938</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AT33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV33" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6818,17 +6785,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6853,90 +6820,179 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>10</v>
+        <v>938</v>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>938</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN34" t="b">
+        <v>1</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6963,17 +7019,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6998,176 +7054,90 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
+        <v>11</v>
+      </c>
+      <c r="O35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7194,17 +7164,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -7229,90 +7199,176 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>7</v>
-      </c>
-      <c r="O36" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q36" t="n">
+        <v>15</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B (bráð, viðvarandi)</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual reported aggregate combining acute and persistent hepatitis B; it is retained as related to course-unspecified D008 but is not interchangeable with a single-course series. Published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN36" t="b">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7374,16 +7430,16 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -7605,19 +7661,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -7750,16 +7806,16 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -7981,19 +8037,19 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O40" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -8126,16 +8182,16 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -8357,19 +8413,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -8502,16 +8558,16 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -8733,19 +8789,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="O44" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -8878,12 +8934,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -9109,19 +9165,19 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O46" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -9254,12 +9310,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -9485,12 +9541,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -9630,12 +9686,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -9861,19 +9917,19 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O50" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -10006,12 +10062,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -10237,19 +10293,19 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -10382,25 +10438,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -10410,7 +10466,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Lifrarbólga B (bráð, viðvarandi)</t>
+          <t>Lifrarbólga B</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -10425,7 +10481,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -10455,7 +10511,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -10470,12 +10526,12 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>IS_DOH_disease_specific_monthly</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual reported aggregate combining acute and persistent hepatitis B; it is retained as related to course-unspecified D008 but is not interchangeable with a single-course series. Published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -10578,17 +10634,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10613,176 +10669,90 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN54" t="b">
+        <v>13</v>
+      </c>
+      <c r="O54" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10809,17 +10779,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -10844,90 +10814,176 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>13</v>
-      </c>
-      <c r="O55" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -10954,17 +11010,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -10989,176 +11045,90 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN56" t="b">
+        <v>13</v>
+      </c>
+      <c r="O56" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11185,17 +11155,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11220,90 +11190,176 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>24</v>
-      </c>
-      <c r="O57" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11330,17 +11386,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11365,176 +11421,90 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN58" t="b">
+        <v>15</v>
+      </c>
+      <c r="O58" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11561,17 +11531,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11596,90 +11566,176 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>7</v>
-      </c>
-      <c r="O59" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11706,17 +11762,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -11741,176 +11797,101 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>801</v>
+      </c>
+      <c r="O60" t="n">
+        <v>801</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
-      <c r="AT60" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV60" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11937,17 +11918,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -11972,90 +11953,179 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>14</v>
+        <v>801</v>
       </c>
       <c r="O61" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>801</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN61" t="b">
+        <v>1</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D49_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12082,17 +12152,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12117,176 +12187,90 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5</v>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Lifrarbólga B</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>related</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>IS_DOH_disease_specific_monthly</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN62" t="b">
+        <v>15</v>
+      </c>
+      <c r="O62" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12313,17 +12297,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12348,90 +12332,176 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>6</v>
-      </c>
-      <c r="O63" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q63" t="n">
+        <v>45</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B (bráð, viðvarandi)</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual reported aggregate combining acute and persistent hepatitis B; it is retained as related to course-unspecified D008 but is not interchangeable with a single-course series. Published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN63" t="b">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -12493,16 +12563,16 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -12724,19 +12794,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O65" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -12869,16 +12939,16 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -13100,19 +13170,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O67" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -13245,16 +13315,16 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -13476,19 +13546,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -13621,16 +13691,16 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -13852,19 +13922,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -13997,16 +14067,16 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -14228,19 +14298,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="O73" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -14373,16 +14443,16 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -14604,12 +14674,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -14749,16 +14819,16 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -14917,6 +14987,1886 @@
         </is>
       </c>
       <c r="BC76" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1999-08</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>12</v>
+      </c>
+      <c r="O77" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1999-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1999-09-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>15</v>
+      </c>
+      <c r="O81" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>20</v>
+      </c>
+      <c r="O83" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>8</v>
+      </c>
+      <c r="O85" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>7</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_HEPATITIS_B_COMBINED_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Lifrarbólga B</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>related</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>IS_DOH_disease_specific_monthly</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Iceland disease-specific monthly registry notifications from the combined hepatitis B workbook; the source does not separate acute and persistent course, so it is related to but not interchangeable with course-unspecified D008. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_ANNUAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
         <is>
           <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
@@ -14967,7 +16917,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
     </row>
@@ -15038,7 +16988,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -15048,7 +16998,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -15068,7 +17018,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -15078,7 +17028,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -15100,7 +17050,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>397</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="16">
